--- a/DataXlCalcNet/DataExamples/MainExamples/Workbooks/XlDemoCPYadv.xlsx
+++ b/DataXlCalcNet/DataExamples/MainExamples/Workbooks/XlDemoCPYadv.xlsx
@@ -8,17 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DUHad\Documents\DataXlCalcNet\DataExamples\MainExamples\Workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38E1CFE-8AEF-4A3D-A5A0-B2DEC2F7B595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0F0E19-02DA-4D78-BFD8-665925F997DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="18923" windowHeight="19928" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18675" yWindow="0" windowWidth="18923" windowHeight="19928" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MpInput" sheetId="6" r:id="rId1"/>
-    <sheet name="Programming" sheetId="4" r:id="rId2"/>
+    <sheet name="FractionsInput" sheetId="6" r:id="rId1"/>
+    <sheet name="DecimalsInput" sheetId="7" r:id="rId2"/>
+    <sheet name="Programming" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="matA">#REF!</definedName>
     <definedName name="matB">#REF!</definedName>
+    <definedName name="MpDecimalsInput">DecimalsInput!$B$3:$B$18</definedName>
+    <definedName name="MpInputDecimals" localSheetId="1">DecimalsInput!$B$3:$B$18</definedName>
+    <definedName name="MpInputFractions">FractionsInput!$B$3:$B$18</definedName>
     <definedName name="PYTHONPATH">#REF!</definedName>
     <definedName name="UPDATE">#REF!</definedName>
   </definedNames>
@@ -65,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>Simple Loop:</t>
   </si>
@@ -82,24 +86,6 @@
     <t>Formatted as Double</t>
   </si>
   <si>
-    <t>123456789012345/678901234567890</t>
-  </si>
-  <si>
-    <t>123456789012345678901/234567890</t>
-  </si>
-  <si>
-    <t>12345678/9012345678901234567890</t>
-  </si>
-  <si>
-    <t>12345678901234/5678901234567890</t>
-  </si>
-  <si>
-    <t>12345678901234567890/1234567890</t>
-  </si>
-  <si>
-    <t>1234567890123456/78901234567890</t>
-  </si>
-  <si>
     <t>XlCalcNet:</t>
   </si>
   <si>
@@ -110,6 +96,105 @@
   </si>
   <si>
     <t>SVG Output written to Output Monitor folder (start Output Monitor first!)</t>
+  </si>
+  <si>
+    <t>123456789012345 / 678901234567890</t>
+  </si>
+  <si>
+    <t>12345678901234 / 5678901234567890</t>
+  </si>
+  <si>
+    <t>123456789012345678901 / 234567890</t>
+  </si>
+  <si>
+    <t>12345678901234567890 / 1234567890</t>
+  </si>
+  <si>
+    <t>1234567890123456 / 78901234567890</t>
+  </si>
+  <si>
+    <t>1234567890123 / 45678901234567890</t>
+  </si>
+  <si>
+    <t>123456 / 789012345678901234567890</t>
+  </si>
+  <si>
+    <t>1234567890123456789012 / 34567890</t>
+  </si>
+  <si>
+    <t>12345678 / 9012345678901234567890</t>
+  </si>
+  <si>
+    <t>1234 / 56789012345678901234567890</t>
+  </si>
+  <si>
+    <t>1234567890123456789012345 / 67890</t>
+  </si>
+  <si>
+    <t>12345678901 / 2345678901234567890</t>
+  </si>
+  <si>
+    <t>12345678901234567 / 8901234567890</t>
+  </si>
+  <si>
+    <t>Prod:</t>
+  </si>
+  <si>
+    <t>Sum:</t>
+  </si>
+  <si>
+    <t>Median:</t>
+  </si>
+  <si>
+    <t>Average:</t>
+  </si>
+  <si>
+    <t>Mean:</t>
+  </si>
+  <si>
+    <t>Variance:</t>
+  </si>
+  <si>
+    <t>Min:</t>
+  </si>
+  <si>
+    <t>Max:</t>
+  </si>
+  <si>
+    <t>123456789012345.678901234567890</t>
+  </si>
+  <si>
+    <t>1234567890123.45678901234567890</t>
+  </si>
+  <si>
+    <t>123456.789012345678901234567890</t>
+  </si>
+  <si>
+    <t>123456789012345678901.234567890</t>
+  </si>
+  <si>
+    <t>1234567890123456789012.34567890</t>
+  </si>
+  <si>
+    <t>1234567890123456.78901234567890</t>
+  </si>
+  <si>
+    <t>12345678.9012345678901234567890</t>
+  </si>
+  <si>
+    <t>12345678901234567.8901234567890</t>
+  </si>
+  <si>
+    <t>12345678901234567890.1234567890</t>
+  </si>
+  <si>
+    <t>1234.56789012345678901234567890</t>
+  </si>
+  <si>
+    <t>1234567890123456789012345.67890</t>
+  </si>
+  <si>
+    <t>12345678901.2345678901234567890</t>
   </si>
 </sst>
 </file>
@@ -147,10 +232,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,163 +553,268 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D2F1AF5-E9DD-47C7-A152-27FF800B6F86}">
-  <dimension ref="A2:B18"/>
+  <dimension ref="A2:C30"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.73046875" customWidth="1"/>
-    <col min="2" max="2" width="21.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" customWidth="1"/>
+    <col min="2" max="2" width="42.73046875" customWidth="1"/>
+    <col min="3" max="3" width="21.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" cm="1">
-        <f t="array" ref="B3">_xll.ASDOUBLE(A3)</f>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" cm="1">
+        <f t="array" ref="C3">_xll.ASDOUBLE(B3)</f>
         <v>2.1739555578260358E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" cm="1">
-        <f t="array" ref="B4">_xll.ASDOUBLE(A4)</f>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" cm="1">
+        <f t="array" ref="C4">_xll.ASDOUBLE(B4)</f>
         <v>0.1818479371169848</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" cm="1">
-        <f t="array" ref="B5">_xll.ASDOUBLE(A5)</f>
-        <v>1.2345678901234568E+29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" cm="1">
-        <f t="array" ref="B6">_xll.ASDOUBLE(A6)</f>
-        <v>1.2345678901234568E+29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" cm="1">
-        <f t="array" ref="B7">_xll.ASDOUBLE(A7)</f>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" cm="1">
+        <f t="array" ref="C5">_xll.ASDOUBLE(B5)</f>
+        <v>2.7027092525350202E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" cm="1">
+        <f t="array" ref="C6">_xll.ASDOUBLE(B6)</f>
+        <v>1.5646903457989998E-19</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2" cm="1">
+        <f t="array" ref="C7">_xll.ASDOUBLE(B7)</f>
         <v>526315809944.5993</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" cm="1">
-        <f t="array" ref="B8">_xll.ASDOUBLE(A8)</f>
-        <v>1.2345678901234568E+29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" cm="1">
-        <f t="array" ref="B9">_xll.ASDOUBLE(A9)</f>
-        <v>1.2345678901234568E+29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="2" cm="1">
-        <f t="array" ref="B10">_xll.ASDOUBLE(A10)</f>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" cm="1">
+        <f t="array" ref="C8">_xll.ASDOUBLE(B8)</f>
+        <v>526315809944.5993</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" cm="1">
+        <f t="array" ref="C9">_xll.ASDOUBLE(B9)</f>
+        <v>35714297000003.664</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2" cm="1">
+        <f t="array" ref="C10">_xll.ASDOUBLE(B10)</f>
+        <v>15.647003457990014</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" cm="1">
+        <f t="array" ref="C11">_xll.ASDOUBLE(B11)</f>
         <v>1.3698629013867518E-15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" cm="1">
-        <f t="array" ref="B11">_xll.ASDOUBLE(A11)</f>
-        <v>1.2345678901234568E+29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="2" cm="1">
-        <f t="array" ref="B12">_xll.ASDOUBLE(A12)</f>
-        <v>1.3698629013867518E-15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="2" cm="1">
+        <f t="array" ref="C12">_xll.ASDOUBLE(B12)</f>
+        <v>1386.9625395301832</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" cm="1">
+        <f t="array" ref="C13">_xll.ASDOUBLE(B13)</f>
+        <v>10000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" cm="1">
+        <f t="array" ref="C14">_xll.ASDOUBLE(B14)</f>
+        <v>15.647003457990014</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="2" cm="1">
+        <f t="array" ref="C15">_xll.ASDOUBLE(B15)</f>
+        <v>2.1729555578261356E-23</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="2" cm="1">
+        <f t="array" ref="C16">_xll.ASDOUBLE(B16)</f>
+        <v>1.8184826780430944E+19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="2" cm="1">
-        <f t="array" ref="B13">_xll.ASDOUBLE(A13)</f>
-        <v>10000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2" cm="1">
-        <f t="array" ref="B14">_xll.ASDOUBLE(A14)</f>
-        <v>15.647003457990014</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" cm="1">
-        <f t="array" ref="B15">_xll.ASDOUBLE(A15)</f>
-        <v>1.2345678901234568E+29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16" s="2" cm="1">
-        <f t="array" ref="B16">_xll.ASDOUBLE(A16)</f>
-        <v>1.2345678901234568E+29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2" cm="1">
-        <f t="array" ref="B17">_xll.ASDOUBLE(A17)</f>
-        <v>1.2345678901234568E+29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B18" s="2" cm="1">
-        <f t="array" ref="B18">_xll.ASDOUBLE(A18)</f>
-        <v>1.2345678901234568E+29</v>
+      <c r="C17" s="2" cm="1">
+        <f t="array" ref="C17">_xll.ASDOUBLE(B17)</f>
+        <v>0.1818479371169848</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" cm="1">
+        <f t="array" ref="C18">_xll.ASDOUBLE(B18)</f>
+        <v>5.2631580965759095E-9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="str" cm="1">
+        <f t="array" ref="B21">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=str(npm.prod(x))",MpInputFractions)</f>
+        <v>190018125514876088955224106518400221345952240439116674051216983384786725609691589863287639839146082672947981737488915381755991008017632869697570716098709604227370512164347238197116336772211981870848/6530618589748757969047941143458327495945465139158098704575064414193558706359502850775410593218609820007999065690593691315922085265330983365667510198760316426280573603112185519094244149744372314453125</v>
+      </c>
+      <c r="C21" cm="1">
+        <f t="array" ref="C21">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=float(npm.prod(x))",MpInputFractions)</f>
+        <v>2.9096497200609958E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="str" cm="1">
+        <f t="array" ref="B22">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=str(npm.sum(x))",MpInputFractions)</f>
+        <v>164496122467480924907368884719850339196807989250775784520809631091899784165891682152271099639262126708760716900236729794313190630035201496706833666597353346491477813015245502446357606/9045771608272968198370581993147209595586077715878587713303230779377072555571602171603483070075220734152954836699083857573183455030428131436190293070332196423447235</v>
+      </c>
+      <c r="C22" cm="1">
+        <f t="array" ref="C22">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=float(npm.sum(x))",MpInputFractions)</f>
+        <v>1.8184863557359565E+19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="str" cm="1">
+        <f t="array" ref="B24">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=str(npm.median(x))",MpInputFractions)</f>
+        <v>1345858028304049186528355603/170051255736733967857203340</v>
+      </c>
+      <c r="C24" cm="1">
+        <f t="array" ref="C24">_xll.ASDOUBLE(B24)</f>
+        <v>7.914425697553499</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="str" cm="1">
+        <f t="array" ref="B25">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=str(npm.average(x))",MpInputFractions)</f>
+        <v>82248061233740462453684442359925169598403994625387892260404815545949892082945841076135549819631063354380358450118364897156595315017600748353416833298676673245738906507622751223178803/72366172866183745586964655945177676764688621727028701706425846235016580444572817372827864560601765873223638693592670860585467640243425051489522344562657571387577880</v>
+      </c>
+      <c r="C25" cm="1">
+        <f t="array" ref="C25">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=float(npm.average(x))",MpInputFractions)</f>
+        <v>1.1365539723349728E+18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="str" cm="1">
+        <f t="array" ref="B26">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=str(npm.mean(x))",MpInputFractions)</f>
+        <v>82248061233740462453684442359925169598403994625387892260404815545949892082945841076135549819631063354380358450118364897156595315017600748353416833298676673245738906507622751223178803/72366172866183745586964655945177676764688621727028701706425846235016580444572817372827864560601765873223638693592670860585467640243425051489522344562657571387577880</v>
+      </c>
+      <c r="C26" cm="1">
+        <f t="array" ref="C26">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=float(npm.mean(x))",MpInputFractions)</f>
+        <v>1.1365539723349728E+18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="str" cm="1">
+        <f t="array" ref="B27">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=str(npm.var(x))",MpInputFractions)</f>
+        <v>101470715860599911527282563915143589066601832998473184214031847149330030490374938574496117829827658303058888910635720340823857268974519451575915748195428419448012870965033329059805527231414189444571812590248238425079942697114172616873641585687069156681937773506057401685115472576997416769703423727393274070044226050638132002375656259186009011920614310200655338243967/5236862975298388583775331619162613737616257482397944211194776444053202104250403274176530041299116449013964372310351469202706807213801580450697301375708670839270417718554707186521953960606903088266544009180217061339249258746686956151403863676667083136537199137209899766804556431228203286842215157516215240068738218475573065294400</v>
+      </c>
+      <c r="C27" cm="1">
+        <f t="array" ref="C27">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=float(npm.var(x))",MpInputFractions)</f>
+        <v>1.9376240382691751E+37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str" cm="1">
+        <f t="array" ref="B29">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=str(npm.min(x))",MpInputFractions)</f>
+        <v>617/28394506172839450617283945</v>
+      </c>
+      <c r="C29" cm="1">
+        <f t="array" ref="C29">_xll.ASDOUBLE(B29)</f>
+        <v>2.1729555578261356E-23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str" cm="1">
+        <f t="array" ref="B30">_xll.CPY_1("from xlcalcnet import npm, qpm $n x = npm.array(P1, dtype=qpm); result=str(npm.max(x))",MpInputFractions)</f>
+        <v>2654984709942917825833/146</v>
+      </c>
+      <c r="C30" cm="1">
+        <f t="array" ref="C30">_xll.ASDOUBLE(B30)</f>
+        <v>1.8184826780430944E+19</v>
       </c>
     </row>
   </sheetData>
@@ -631,6 +824,278 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07057DC0-2466-42B9-8288-6D266B82EB11}">
+  <dimension ref="A2:C30"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.59765625" customWidth="1"/>
+    <col min="2" max="2" width="42.73046875" customWidth="1"/>
+    <col min="3" max="3" width="24.06640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="2" cm="1">
+        <f t="array" ref="C3">_xll.ASDOUBLE(B3)</f>
+        <v>1234.5678901234569</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" cm="1">
+        <f t="array" ref="C4">_xll.ASDOUBLE(B4)</f>
+        <v>1.2345678901234568E+29</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" cm="1">
+        <f t="array" ref="C5">_xll.ASDOUBLE(B5)</f>
+        <v>1234567890123.4568</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2" cm="1">
+        <f t="array" ref="C6">_xll.ASDOUBLE(B6)</f>
+        <v>123456.78901234567</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" cm="1">
+        <f t="array" ref="C7">_xll.ASDOUBLE(B7)</f>
+        <v>1.2345678901234568E+20</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="2" cm="1">
+        <f t="array" ref="C8">_xll.ASDOUBLE(B8)</f>
+        <v>1.2345678901234568E+20</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2" cm="1">
+        <f t="array" ref="C9">_xll.ASDOUBLE(B9)</f>
+        <v>1.2345678901234568E+21</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="2" cm="1">
+        <f t="array" ref="C10">_xll.ASDOUBLE(B10)</f>
+        <v>1234567890123456.8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" cm="1">
+        <f t="array" ref="C11">_xll.ASDOUBLE(B11)</f>
+        <v>12345678.901234567</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2" cm="1">
+        <f t="array" ref="C12">_xll.ASDOUBLE(B12)</f>
+        <v>1.2345678901234568E+16</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="2" cm="1">
+        <f t="array" ref="C13">_xll.ASDOUBLE(B13)</f>
+        <v>1.2345678901234567E+19</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" cm="1">
+        <f t="array" ref="C14">_xll.ASDOUBLE(B14)</f>
+        <v>1234567890123456.8</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" cm="1">
+        <f t="array" ref="C15">_xll.ASDOUBLE(B15)</f>
+        <v>1234.5678901234569</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2" cm="1">
+        <f t="array" ref="C16">_xll.ASDOUBLE(B16)</f>
+        <v>1.2345678901234568E+24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="2" cm="1">
+        <f t="array" ref="C17">_xll.ASDOUBLE(B17)</f>
+        <v>123456789012345.67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="2" cm="1">
+        <f t="array" ref="C18">_xll.ASDOUBLE(B18)</f>
+        <v>12345678901.234568</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="str" cm="1">
+        <f t="array" ref="B21">_xll.CPY_1("from xlcalcnet import npm, dpm $n dpm.dps = 30; x = npm.array(P1, dtype=dpm); result=str(npm.prod(x))",MpInputDecimals)</f>
+        <v>2.91232363938162659138272892973E+234</v>
+      </c>
+      <c r="C21" s="2" cm="1">
+        <f t="array" ref="C21">_xll.ASDOUBLE(B21)</f>
+        <v>2.9123236393816265E+234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="str" cm="1">
+        <f t="array" ref="B22">_xll.CPY_1("from xlcalcnet import npm, dpm $n dpm.dps = 30; x = npm.array(P1, dtype=dpm); result=str(npm.sum(x))",MpInputDecimals)</f>
+        <v>123458025074077888925802829398</v>
+      </c>
+      <c r="C22" s="2" cm="1">
+        <f t="array" ref="C22">_xll.ASDOUBLE(B22)</f>
+        <v>1.2345802507407789E+29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="str" cm="1">
+        <f t="array" ref="B24">_xll.CPY_1("from xlcalcnet import npm, dpm $n dpm.dps = 30; x = npm.array(P1, dtype=dpm); result=str(npm.median(x))",MpInputDecimals)</f>
+        <v>1234567890123456.78901234567890</v>
+      </c>
+      <c r="C24" s="2" cm="1">
+        <f t="array" ref="C24">_xll.ASDOUBLE(B24)</f>
+        <v>1234567890123456.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="str" cm="1">
+        <f t="array" ref="B25">_xll.CPY_1("from xlcalcnet import npm, dpm $n dpm.dps = 30; x = npm.array(P1, dtype=dpm); result=str(npm.average(x))",MpInputDecimals)</f>
+        <v>7716126567129868057862676837.38</v>
+      </c>
+      <c r="C25" s="2" cm="1">
+        <f t="array" ref="C25">_xll.ASDOUBLE(B25)</f>
+        <v>7.7161265671298682E+27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="str" cm="1">
+        <f t="array" ref="B26">_xll.CPY_1("from xlcalcnet import npm, dpm $n dpm.dps = 30; x = npm.array(P1, dtype=dpm); result=str(npm.mean(x))",MpInputDecimals)</f>
+        <v>7716126567129868057862676837.38</v>
+      </c>
+      <c r="C26" s="2" cm="1">
+        <f t="array" ref="C26">_xll.ASDOUBLE(B26)</f>
+        <v>7.7161265671298682E+27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="str" cm="1">
+        <f t="array" ref="B27">_xll.CPY_1("from xlcalcnet import npm, dpm $n dpm.dps = 30; x = npm.array(P1, dtype=dpm); result=str(npm.var(x))",MpInputDecimals)</f>
+        <v>8.93060062972719899056318097025E+56</v>
+      </c>
+      <c r="C27" s="2" cm="1">
+        <f t="array" ref="C27">_xll.ASDOUBLE(B27)</f>
+        <v>8.930600629727199E+56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str" cm="1">
+        <f t="array" ref="B29">_xll.CPY_1("from xlcalcnet import npm, dpm $n dpm.dps = 30; x = npm.array(P1, dtype=dpm); result=str(npm.mean(x))",MpInputDecimals)</f>
+        <v>7716126567129868057862676837.38</v>
+      </c>
+      <c r="C29" s="2" cm="1">
+        <f t="array" ref="C29">_xll.ASDOUBLE(B29)</f>
+        <v>7.7161265671298682E+27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str" cm="1">
+        <f t="array" ref="B30">_xll.CPY_1("from xlcalcnet import npm, dpm $n dpm.dps = 30; x = npm.array(P1, dtype=dpm); result=str(npm.max(x))",MpInputDecimals)</f>
+        <v>123456789012345678901234567890</v>
+      </c>
+      <c r="C30" s="2" cm="1">
+        <f t="array" ref="C30">_xll.ASDOUBLE(B30)</f>
+        <v>1.2345678901234568E+29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:C22"/>
   <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
@@ -663,7 +1128,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -674,18 +1139,18 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
-        <f>_xll.CPY_0("from scipy.integrate import quad $n def integrand(x, a, b): return a*x**2 + b $n a = 2.1; b = 1.1;  $n I = quad(integrand, 0, 1, args=(a,b))   $n result = str(I) ")</f>
+        <f>_xll.CPY_0("from scipy.integrate import quad $n def integrand(x, a, b): return  a*x**2 + b $n a = 2.1; b = 1.1;  $n I = quad(integrand, 0, 1, args=(a,b))   $n result = str(I) ")</f>
         <v>Exception: No module named 'scipy'</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
@@ -696,7 +1161,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">

--- a/DataXlCalcNet/DataExamples/MainExamples/Workbooks/XlDemoCPYadv.xlsx
+++ b/DataXlCalcNet/DataExamples/MainExamples/Workbooks/XlDemoCPYadv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DUHad\Documents\DataXlCalcNet\DataExamples\MainExamples\Workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{92A485D7-2DE7-4F39-8A61-7A4DD1518B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5809F21-63A1-4F41-BC65-9739CEB7A581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="18923" windowHeight="19928" firstSheet="1" activeTab="3" xr2:uid="{35C406F7-5A1B-48FB-8DEC-8B4643AB952A}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="18923" windowHeight="19928" firstSheet="1" activeTab="4" xr2:uid="{35C406F7-5A1B-48FB-8DEC-8B4643AB952A}"/>
   </bookViews>
   <sheets>
     <sheet name="FractionsInput" sheetId="1" r:id="rId1"/>
@@ -1484,7 +1484,7 @@
         <v>Python Script:</v>
       </c>
       <c r="B1" s="1" t="str" cm="1">
-        <f t="array" ref="B1">_xll.CPY_0(_xlfn.TEXTJOIN(" ",1,"from A06_UserlibExamplesPython.B29_InferentialStatistics.C01_BasicTests1Sample import D01_StudentT_PValues $n D01_StudentT_PValues.stats_student_t_1sample_test(n=",B3,", mu0=",B4,", mean=",B5,", std=",B6,", alpha=", B7, B8, ")"," $n result='Students t-test, 1 sample'"))</f>
+        <f t="array" ref="B1">_xll.CPY_0(_xlfn.TEXTJOIN(" ",1,"from A06_UserlibExamplesPython.B29_InferentialStatistics.C01_BasicTests1Sample import D01_StudentT_PValues $n importlib.reload(D01_StudentT_PValues) $n  D01_StudentT_PValues.stats_student_t_1sample_test(n=",B3,", mu0=",B4,", mean=",B5,", std=",B6,", alpha=", B7, B8, ")"," $n result='Students t-test, 1 sample'"))</f>
         <v>Students t-test, 1 sample</v>
       </c>
       <c r="C1" s="1"/>
@@ -1836,7 +1836,7 @@
         <v>Python Script:</v>
       </c>
       <c r="B1" s="1" t="str" cm="1">
-        <f t="array" ref="B1">_xll.CPY_0(_xlfn.TEXTJOIN(" ",1,"from A01_ExamplesPython.B18_FunctionsAndCurvesPlots.C01_Intro_Parametric2D import D07_DistPlotContinuous $n D07_DistPlotContinuous.DistPlotBeta(target=",B3,", a=",B4,", b=",B5,", Title=",B6,", OutputMode = 'svg'",  ")"," $n result='Beta distribution'"))</f>
+        <f t="array" ref="B1">_xll.CPY_0(_xlfn.TEXTJOIN(" ",1,"from A01_ExamplesPython.B18_FunctionsAndCurvesPlots.C01_Intro_Parametric2D import D07_DistPlotContinuous $n importlib.reload(D07_DistPlotContinuous) $n   D07_DistPlotContinuous.DistPlotBeta(target=",B3,", a=",B4,", b=",B5,", Title=",B6,", OutputMode = 'svg'",  ")"," $n result='Beta distribution'"))</f>
         <v>Beta distribution</v>
       </c>
       <c r="C1" s="1"/>
@@ -1865,8 +1865,8 @@
         <v>a:</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>"[5, 10.0, 20.5]"</f>
-        <v>[5, 10.0, 20.5]</v>
+        <f>"[15, 10.0, 20.5]"</f>
+        <v>[15, 10.0, 20.5]</v>
       </c>
       <c r="C4" s="1"/>
     </row>
